--- a/data/mini-example-resilience/Power_Tec.xlsx
+++ b/data/mini-example-resilience/Power_Tec.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\LEGO-Pyomo\data\example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{672D846F-72A8-4773-B067-FAC1CC39C10B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B49213C2-A3C7-478A-8C3A-2DA293D4349F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36210" yWindow="1650" windowWidth="28800" windowHeight="15240" tabRatio="958" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="958" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Power Tec" sheetId="112" r:id="rId1"/>
@@ -98,9 +98,6 @@
     <t>FACTS</t>
   </si>
   <si>
-    <t>Nuclear</t>
-  </si>
-  <si>
     <t>FuelOilGas</t>
   </si>
   <si>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t>Power Technologies</t>
+  </si>
+  <si>
+    <t>BackupGenerator</t>
   </si>
 </sst>
 </file>
@@ -619,19 +619,19 @@
     <tabColor rgb="FF008080"/>
   </sheetPr>
   <dimension ref="A1:AKU14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="13" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="42.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="983" width="11.3984375" style="2"/>
+    <col min="1" max="1" width="2.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="42.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="983" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:983" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:983" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:983" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:983" x14ac:dyDescent="0.2">
       <c r="A2"/>
       <c r="B2"/>
       <c r="C2"/>
@@ -1616,7 +1616,7 @@
       <c r="AKT2"/>
       <c r="AKU2"/>
     </row>
-    <row r="3" spans="1:983" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:983" x14ac:dyDescent="0.2">
       <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
@@ -2602,9 +2602,9 @@
       <c r="AKT3"/>
       <c r="AKU3"/>
     </row>
-    <row r="4" spans="1:983" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:983" x14ac:dyDescent="0.2">
       <c r="B4" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4"/>
       <c r="D4"/>
@@ -3588,52 +3588,52 @@
       <c r="AKT4"/>
       <c r="AKU4"/>
     </row>
-    <row r="5" spans="1:983" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:983" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:983" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:983" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:983" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:983" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:983" x14ac:dyDescent="0.45">
-      <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:983" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:983" x14ac:dyDescent="0.2">
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:983" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:983" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:983" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:983" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:983" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:983" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:983" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:983" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:983" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:983" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:983" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
@@ -3646,12 +3646,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3801,15 +3798,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13778B2C-CE05-4B32-8196-2F381FEAC95A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0155F7A0-74CD-4575-8C0B-A34C113F80FE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="87003a75-b64f-4b22-bf19-aa30740e3d46"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3833,17 +3841,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0155F7A0-74CD-4575-8C0B-A34C113F80FE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13778B2C-CE05-4B32-8196-2F381FEAC95A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="87003a75-b64f-4b22-bf19-aa30740e3d46"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>